--- a/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_ADO.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_ADO.xlsx
@@ -13,8 +13,8 @@
     <sheet name="duos_trios" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$A$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$B$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'key_lineups'!$A$1:$A$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'duos_trios'!$A$1:$J$7</definedName>
   </definedNames>
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -458,7 +458,11 @@
           <t>team_name</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>AD Ovarense</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -468,36 +472,72 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>best_duo</t>
+          <t>primary_scorer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>L. Ayers | R. Soeiro (-2.2 net)</t>
+          <t>L. Ayers (24.5 ppg)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>most_used_player</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>L. Ayers (26.3 mpg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>best_3pt_pct</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>R. Soeiro (66.7%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>best_duo</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>L. Ayers | R. Soeiro (3.6 net)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>best_trio</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>L. Ayers | M. Monteiro | R. Soeiro (19.1 net)</t>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>D. Cambridge | L. Ayers | R. Soeiro (-4.2 net)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B6"/>
+  <autoFilter ref="A1:B9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -508,28 +548,627 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:U7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="23" customWidth="1" min="20" max="20"/>
+    <col width="41" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>team_name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>playing_position</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>games</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>games_started</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>minutes_total</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>mpg</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ppg</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>rpg</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>apg</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>tov_pg</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>spg</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>bpg</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>fg_pct</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>tp_pct</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>ft_pct</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>efg_pct</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ts_pct</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>plus_minus_pg</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>on_off_net_diff_per40</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>role_tag</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
+          <t>AD Ovarense</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>L. Ayers</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>52.5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="H2" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>60.9%</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>65.7%</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="T2" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>high-minutes, primary-scorer, efficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>AD Ovarense</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>D. Cambridge</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>47.6%</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>52.4%</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>50.1%</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-29.4</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>primary-scorer</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>AD Ovarense</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>R. Soeiro</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>88.8%</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-27.6</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>efficient, shooter</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AD Ovarense</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>R. Woods</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="G5" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>8</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J5" t="n">
+        <v>7</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>13</v>
+      </c>
+      <c r="T5" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>shooter, impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AD Ovarense</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>L. Boyle</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="G6" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>7</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>45.8%</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>49.3%</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="T6" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AD Ovarense</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>J. Wood</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>20.3</v>
+      </c>
+      <c r="H7" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>43.8%</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>56.2%</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>57.8%</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="T7" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>shooter, impact</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A2"/>
+  <autoFilter ref="A1:U7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -578,7 +1217,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="37" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -661,22 +1300,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="G2" t="n">
-        <v>18.6</v>
+        <v>33.7</v>
       </c>
       <c r="H2" t="n">
-        <v>81.90000000000001</v>
+        <v>80.8</v>
       </c>
       <c r="I2" t="n">
-        <v>84</v>
+        <v>77.2</v>
       </c>
       <c r="J2" t="n">
-        <v>-2.2</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="3">
@@ -697,26 +1336,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>L. Boyle | M. Monteiro</t>
+          <t>L. Ayers | L. Boyle</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G3" t="n">
-        <v>18.4</v>
+        <v>29.1</v>
       </c>
       <c r="H3" t="n">
-        <v>88.90000000000001</v>
+        <v>104.3</v>
       </c>
       <c r="I3" t="n">
-        <v>52</v>
+        <v>57.7</v>
       </c>
       <c r="J3" t="n">
-        <v>36.9</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="4">
@@ -737,26 +1376,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>L. Boyle | M. Monteiro</t>
+          <t>L. Ayers | L. Boyle</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G4" t="n">
-        <v>18.4</v>
+        <v>29.1</v>
       </c>
       <c r="H4" t="n">
-        <v>88.90000000000001</v>
+        <v>104.3</v>
       </c>
       <c r="I4" t="n">
-        <v>52</v>
+        <v>57.7</v>
       </c>
       <c r="J4" t="n">
-        <v>36.9</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="5">
@@ -777,26 +1416,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>L. Ayers | M. Monteiro | R. Soeiro</t>
+          <t>D. Cambridge | L. Ayers | R. Soeiro</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G5" t="n">
-        <v>14.7</v>
+        <v>19.2</v>
       </c>
       <c r="H5" t="n">
-        <v>98.2</v>
+        <v>66.8</v>
       </c>
       <c r="I5" t="n">
-        <v>79.09999999999999</v>
+        <v>71</v>
       </c>
       <c r="J5" t="n">
-        <v>19.1</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="6">
@@ -817,26 +1456,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>J. Wood | N. Morais | R. Woods</t>
+          <t>J. Silva | L. Ayers | R. Woods</t>
         </is>
       </c>
       <c r="E6" t="n">
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G6" t="n">
-        <v>12.7</v>
+        <v>17.1</v>
       </c>
       <c r="H6" t="n">
-        <v>119.4</v>
+        <v>117.3</v>
       </c>
       <c r="I6" t="n">
-        <v>81.7</v>
+        <v>72.7</v>
       </c>
       <c r="J6" t="n">
-        <v>37.7</v>
+        <v>44.6</v>
       </c>
     </row>
     <row r="7">
@@ -861,22 +1500,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G7" t="n">
-        <v>14.4</v>
+        <v>18.5</v>
       </c>
       <c r="H7" t="n">
-        <v>94.40000000000001</v>
+        <v>95</v>
       </c>
       <c r="I7" t="n">
-        <v>61.1</v>
+        <v>56.1</v>
       </c>
       <c r="J7" t="n">
-        <v>33.3</v>
+        <v>38.8</v>
       </c>
     </row>
   </sheetData>

--- a/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_ADO.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_ADO.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$B$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'key_lineups'!$A$1:$A$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'duos_trios'!$A$1:$J$7</definedName>
   </definedNames>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>L. Ayers (24.5 ppg)</t>
+          <t>L. Ayers (22 ppg)</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>L. Ayers (26.3 mpg)</t>
+          <t>L. Ayers (27.3 mpg)</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>R. Soeiro (66.7%)</t>
+          <t>L. Ayers (47.1%)</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>L. Ayers | R. Soeiro (3.6 net)</t>
+          <t>L. Ayers | R. Soeiro (7.8 net)</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>D. Cambridge | L. Ayers | R. Soeiro (-4.2 net)</t>
+          <t>L. Ayers | L. Boyle | M. Monteiro (28.3 net)</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U7"/>
+  <dimension ref="A1:U11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -698,65 +698,65 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>52.5</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>26.3</v>
+        <v>27.3</v>
       </c>
       <c r="H2" t="n">
-        <v>24.5</v>
+        <v>22</v>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>6.3</v>
       </c>
       <c r="J2" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="K2" t="n">
         <v>3</v>
       </c>
       <c r="L2" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>60.9%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>14.5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="n">
-        <v>22.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -777,53 +777,53 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>47.5</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>23.7</v>
       </c>
       <c r="H3" t="n">
-        <v>12.5</v>
+        <v>11.3</v>
       </c>
       <c r="I3" t="n">
-        <v>8.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
           <t>33.3%</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>51.7%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -832,14 +832,14 @@
         </is>
       </c>
       <c r="S3" t="n">
-        <v>2.5</v>
+        <v>3.7</v>
       </c>
       <c r="T3" t="n">
-        <v>-29.4</v>
+        <v>-22.8</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>primary-scorer</t>
+          <t>rotation</t>
         </is>
       </c>
     </row>
@@ -860,43 +860,43 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>43.4</v>
+        <v>60.2</v>
       </c>
       <c r="G4" t="n">
-        <v>21.7</v>
+        <v>20.1</v>
       </c>
       <c r="H4" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="K4" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -906,19 +906,19 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>88.8%</t>
+          <t>60.9%</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="T4" t="n">
-        <v>-27.6</v>
+        <v>-16.1</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>R. Woods</t>
+          <t>M. Monteiro</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -943,65 +943,69 @@
         </is>
       </c>
       <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="n">
         <v>2</v>
       </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
       <c r="F5" t="n">
-        <v>40.9</v>
+        <v>59.9</v>
       </c>
       <c r="G5" t="n">
-        <v>20.5</v>
+        <v>20</v>
       </c>
       <c r="H5" t="n">
-        <v>8</v>
+        <v>6.3</v>
       </c>
       <c r="I5" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="J5" t="n">
-        <v>7</v>
+        <v>4.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5</v>
+        <v>2.3</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>44.4%</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr"/>
+          <t>20.0%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>26.3</v>
+        <v>9.4</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>shooter, impact</t>
+          <t>impact</t>
         </is>
       </c>
     </row>
@@ -1013,74 +1017,78 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>L. Boyle</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>R. Woods</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>40.9</v>
+        <v>59.4</v>
       </c>
       <c r="G6" t="n">
-        <v>20.5</v>
+        <v>19.8</v>
       </c>
       <c r="H6" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" t="n">
         <v>7</v>
       </c>
-      <c r="I6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
       <c r="K6" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>19.5</v>
+        <v>10.3</v>
       </c>
       <c r="T6" t="n">
-        <v>42.4</v>
+        <v>18.9</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>impact</t>
+          <t>shooter, impact</t>
         </is>
       </c>
     </row>
@@ -1101,74 +1109,390 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>40.5</v>
+        <v>58</v>
       </c>
       <c r="G7" t="n">
-        <v>20.3</v>
+        <v>19.3</v>
       </c>
       <c r="H7" t="n">
-        <v>9.5</v>
+        <v>8</v>
       </c>
       <c r="I7" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>54.8%</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>56.0%</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>shooter</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AD Ovarense</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>L. Boyle</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" t="n">
+        <v>56.5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>18.8</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>34.4%</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>29.6</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AD Ovarense</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>N. Morais</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>51.1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>17</v>
+      </c>
+      <c r="H9" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>63.5%</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="T9" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>efficient, shooter, impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>AD Ovarense</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>J. Palm</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
         <v>1</v>
       </c>
-      <c r="L7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>43.8%</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>40.0%</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>100.0%</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>56.2%</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>57.8%</t>
-        </is>
-      </c>
-      <c r="S7" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>12.6</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>shooter, impact</t>
+      <c r="F10" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="H10" t="n">
+        <v>13</v>
+      </c>
+      <c r="I10" t="n">
+        <v>6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>63.7%</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>8</v>
+      </c>
+      <c r="T10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>primary-scorer, efficient, impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>AD Ovarense</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>J. Silva</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="n">
+        <v>40.2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>9</v>
+      </c>
+      <c r="I11" t="n">
+        <v>10</v>
+      </c>
+      <c r="J11" t="n">
+        <v>2</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>47.1%</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>47.1%</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>45.8%</t>
+        </is>
+      </c>
+      <c r="S11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>rotation</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U7"/>
+  <autoFilter ref="A1:U11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1217,7 +1541,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="37" customWidth="1" min="4" max="4"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -1300,22 +1624,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G2" t="n">
-        <v>33.7</v>
+        <v>46.1</v>
       </c>
       <c r="H2" t="n">
-        <v>80.8</v>
+        <v>77.3</v>
       </c>
       <c r="I2" t="n">
-        <v>77.2</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="3">
@@ -1340,22 +1664,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G3" t="n">
-        <v>29.1</v>
+        <v>41.5</v>
       </c>
       <c r="H3" t="n">
-        <v>104.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>57.7</v>
+        <v>55.9</v>
       </c>
       <c r="J3" t="n">
-        <v>46.7</v>
+        <v>34.7</v>
       </c>
     </row>
     <row r="4">
@@ -1380,22 +1704,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G4" t="n">
-        <v>29.1</v>
+        <v>41.5</v>
       </c>
       <c r="H4" t="n">
-        <v>104.3</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>57.7</v>
+        <v>55.9</v>
       </c>
       <c r="J4" t="n">
-        <v>46.7</v>
+        <v>34.7</v>
       </c>
     </row>
     <row r="5">
@@ -1416,26 +1740,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>D. Cambridge | L. Ayers | R. Soeiro</t>
+          <t>L. Ayers | L. Boyle | M. Monteiro</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G5" t="n">
-        <v>19.2</v>
+        <v>29.7</v>
       </c>
       <c r="H5" t="n">
-        <v>66.8</v>
+        <v>82.2</v>
       </c>
       <c r="I5" t="n">
-        <v>71</v>
+        <v>53.9</v>
       </c>
       <c r="J5" t="n">
-        <v>-4.2</v>
+        <v>28.3</v>
       </c>
     </row>
     <row r="6">
@@ -1456,26 +1780,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>J. Silva | L. Ayers | R. Woods</t>
+          <t>J. Silva | L. Ayers | L. Boyle</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G6" t="n">
-        <v>17.1</v>
+        <v>24.3</v>
       </c>
       <c r="H6" t="n">
-        <v>117.3</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>72.7</v>
+        <v>52.6</v>
       </c>
       <c r="J6" t="n">
-        <v>44.6</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="7">
@@ -1496,26 +1820,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>L. Ayers | L. Boyle | M. Monteiro</t>
+          <t>J. Silva | L. Ayers | L. Boyle</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G7" t="n">
-        <v>18.5</v>
+        <v>24.3</v>
       </c>
       <c r="H7" t="n">
-        <v>95</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>56.1</v>
+        <v>52.6</v>
       </c>
       <c r="J7" t="n">
-        <v>38.8</v>
+        <v>34.5</v>
       </c>
     </row>
   </sheetData>

--- a/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_ADO.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_ADO.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>L. Ayers (22 ppg)</t>
+          <t>L. Ayers (22.5 ppg)</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>L. Ayers (27.3 mpg)</t>
+          <t>L. Ayers (28.8 mpg)</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>L. Ayers (47.1%)</t>
+          <t>L. Ayers (47.8%)</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>L. Ayers | R. Soeiro (7.8 net)</t>
+          <t>D. Cambridge | L. Ayers (2.7 net)</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>L. Ayers | L. Boyle | M. Monteiro (28.3 net)</t>
+          <t>D. Cambridge | J. Wood | L. Ayers (-6.1 net)</t>
         </is>
       </c>
     </row>
@@ -698,65 +698,65 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>81.90000000000001</v>
+        <v>115.2</v>
       </c>
       <c r="G2" t="n">
-        <v>27.3</v>
+        <v>28.8</v>
       </c>
       <c r="H2" t="n">
-        <v>22</v>
+        <v>22.5</v>
       </c>
       <c r="I2" t="n">
-        <v>6.3</v>
+        <v>5.8</v>
       </c>
       <c r="J2" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="K2" t="n">
         <v>3</v>
       </c>
       <c r="L2" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>9.300000000000001</v>
+        <v>15.3</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -777,69 +777,69 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
+        <v>4</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>102.5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="H3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K3" t="n">
         <v>3</v>
       </c>
-      <c r="E3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>71.09999999999999</v>
-      </c>
-      <c r="G3" t="n">
-        <v>23.7</v>
-      </c>
-      <c r="H3" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="I3" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>2.7</v>
-      </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>52.9%</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>51.7%</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>50.1%</t>
-        </is>
-      </c>
       <c r="S3" t="n">
-        <v>3.7</v>
+        <v>2.5</v>
       </c>
       <c r="T3" t="n">
-        <v>-22.8</v>
+        <v>-17</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>rotation</t>
+          <t>high-minutes</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>R. Soeiro</t>
+          <t>J. Wood</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -860,69 +860,69 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>60.2</v>
+        <v>85.8</v>
       </c>
       <c r="G4" t="n">
-        <v>20.1</v>
+        <v>21.5</v>
       </c>
       <c r="H4" t="n">
+        <v>8</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>40.6%</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>27.8%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>48.4%</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>49.3%</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
         <v>5</v>
       </c>
-      <c r="I4" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>45.5%</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>44.4%</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>63.6%</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>60.9%</t>
-        </is>
-      </c>
-      <c r="S4" t="n">
-        <v>1.7</v>
-      </c>
       <c r="T4" t="n">
-        <v>-16.1</v>
+        <v>0.1</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>efficient, shooter</t>
+          <t>rotation</t>
         </is>
       </c>
     </row>
@@ -943,69 +943,69 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
         <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>59.9</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>20</v>
+        <v>20.6</v>
       </c>
       <c r="H5" t="n">
-        <v>6.3</v>
+        <v>7</v>
       </c>
       <c r="I5" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K5" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>9.300000000000001</v>
+        <v>4</v>
       </c>
       <c r="T5" t="n">
-        <v>9.4</v>
+        <v>-4.1</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>impact</t>
+          <t>rotation</t>
         </is>
       </c>
     </row>
@@ -1026,65 +1026,65 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>80.09999999999999</v>
+      </c>
+      <c r="G6" t="n">
+        <v>20</v>
+      </c>
+      <c r="H6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K6" t="n">
         <v>1</v>
       </c>
-      <c r="F6" t="n">
-        <v>59.4</v>
-      </c>
-      <c r="G6" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="H6" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="I6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J6" t="n">
-        <v>7</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.7</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>10.3</v>
+        <v>9.5</v>
       </c>
       <c r="T6" t="n">
-        <v>18.9</v>
+        <v>21.5</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
@@ -1100,78 +1100,78 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>J. Wood</t>
+          <t>R. Soeiro</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" t="n">
         <v>3</v>
       </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
       <c r="F7" t="n">
-        <v>58</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>19.3</v>
+        <v>17.3</v>
       </c>
       <c r="H7" t="n">
-        <v>8</v>
+        <v>3.8</v>
       </c>
       <c r="I7" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>6.7</v>
+        <v>2</v>
       </c>
       <c r="T7" t="n">
-        <v>3.5</v>
+        <v>-6.1</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>shooter</t>
+          <t>rotation</t>
         </is>
       </c>
     </row>
@@ -1188,43 +1188,43 @@
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E8" t="n">
         <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>56.5</v>
+        <v>66.8</v>
       </c>
       <c r="G8" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="H8" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="I8" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1234,19 +1234,19 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>14.3</v>
+        <v>9.5</v>
       </c>
       <c r="T8" t="n">
-        <v>29.6</v>
+        <v>18</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
@@ -1262,37 +1262,33 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>N. Morais</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
+          <t>J. Palm</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
         <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>51.1</v>
+        <v>64</v>
       </c>
       <c r="G9" t="n">
-        <v>17</v>
+        <v>21.3</v>
       </c>
       <c r="H9" t="n">
+        <v>10</v>
+      </c>
+      <c r="I9" t="n">
         <v>6.7</v>
       </c>
-      <c r="I9" t="n">
-        <v>2</v>
-      </c>
       <c r="J9" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="L9" t="n">
         <v>0.3</v>
@@ -1302,38 +1298,34 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>36.4%</t>
-        </is>
-      </c>
+          <t>63.2%</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>8.699999999999999</v>
+        <v>3.7</v>
       </c>
       <c r="T9" t="n">
-        <v>13.4</v>
+        <v>6.4</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>efficient, shooter, impact</t>
+          <t>efficient, impact</t>
         </is>
       </c>
     </row>
@@ -1345,43 +1337,47 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>J. Palm</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>J. Silva</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="G10" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="H10" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="I10" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M10" t="n">
         <v>1</v>
       </c>
-      <c r="F10" t="n">
-        <v>47.1</v>
-      </c>
-      <c r="G10" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="H10" t="n">
-        <v>13</v>
-      </c>
-      <c r="I10" t="n">
-        <v>6</v>
-      </c>
-      <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -1392,23 +1388,23 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>6.7</v>
       </c>
       <c r="T10" t="n">
-        <v>12.5</v>
+        <v>4.9</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>primary-scorer, efficient, impact</t>
+          <t>rotation</t>
         </is>
       </c>
     </row>
@@ -1420,74 +1416,78 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>J. Silva</t>
+          <t>N. Morais</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>G</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>40.2</v>
+        <v>57.8</v>
       </c>
       <c r="G11" t="n">
-        <v>20.1</v>
+        <v>14.4</v>
       </c>
       <c r="H11" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>10</v>
+        <v>1.5</v>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="K11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>47.1%</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr"/>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>36.4%</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="S11" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="T11" t="n">
-        <v>-5.1</v>
+        <v>5</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>rotation</t>
+          <t>efficient, shooter, impact</t>
         </is>
       </c>
     </row>
@@ -1620,26 +1620,26 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>L. Ayers | R. Soeiro</t>
+          <t>D. Cambridge | L. Ayers</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="G2" t="n">
-        <v>46.1</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>77.3</v>
+        <v>81.2</v>
       </c>
       <c r="I2" t="n">
-        <v>69.40000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="J2" t="n">
-        <v>7.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="3">
@@ -1664,22 +1664,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G3" t="n">
-        <v>41.5</v>
+        <v>45.2</v>
       </c>
       <c r="H3" t="n">
-        <v>90.59999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="I3" t="n">
-        <v>55.9</v>
+        <v>58.5</v>
       </c>
       <c r="J3" t="n">
-        <v>34.7</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="4">
@@ -1704,22 +1704,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G4" t="n">
-        <v>41.5</v>
+        <v>45.2</v>
       </c>
       <c r="H4" t="n">
-        <v>90.59999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="I4" t="n">
-        <v>55.9</v>
+        <v>58.5</v>
       </c>
       <c r="J4" t="n">
-        <v>34.7</v>
+        <v>32.8</v>
       </c>
     </row>
     <row r="5">
@@ -1740,26 +1740,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>L. Ayers | L. Boyle | M. Monteiro</t>
+          <t>D. Cambridge | J. Wood | L. Ayers</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G5" t="n">
-        <v>29.7</v>
+        <v>45.7</v>
       </c>
       <c r="H5" t="n">
-        <v>82.2</v>
+        <v>70</v>
       </c>
       <c r="I5" t="n">
-        <v>53.9</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>28.3</v>
+        <v>-6.1</v>
       </c>
     </row>
     <row r="6">
@@ -1780,26 +1780,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>J. Silva | L. Ayers | L. Boyle</t>
+          <t>L. Ayers | L. Boyle | M. Monteiro</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F6" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G6" t="n">
-        <v>24.3</v>
+        <v>31.6</v>
       </c>
       <c r="H6" t="n">
-        <v>87.09999999999999</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>52.6</v>
+        <v>59.6</v>
       </c>
       <c r="J6" t="n">
-        <v>34.5</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="7">
@@ -1820,26 +1820,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>J. Silva | L. Ayers | L. Boyle</t>
+          <t>L. Ayers | L. Boyle | M. Monteiro</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G7" t="n">
-        <v>24.3</v>
+        <v>31.6</v>
       </c>
       <c r="H7" t="n">
-        <v>87.09999999999999</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>52.6</v>
+        <v>59.6</v>
       </c>
       <c r="J7" t="n">
-        <v>34.5</v>
+        <v>20.3</v>
       </c>
     </row>
   </sheetData>
